--- a/Atlas/Dog/Johnson_dictionary.xlsx
+++ b/Atlas/Dog/Johnson_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\dog_brain_toolkit\Atlas\Dog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9537FF79-B3F2-480B-874C-9D8EFC633D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF290E92-BB41-4EFF-BC11-E89A8A0D6A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,9 +43,6 @@
     <t>Hemisphere</t>
   </si>
   <si>
-    <t>Abreviation</t>
-  </si>
-  <si>
     <t>CN_FCM_L.nii.gz</t>
   </si>
   <si>
@@ -1922,6 +1919,9 @@
   </si>
   <si>
     <t>Lobe_Number</t>
+  </si>
+  <si>
+    <t>Abbreviation</t>
   </si>
 </sst>
 </file>
@@ -2311,13 +2311,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -2326,10 +2326,10 @@
         <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>632</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2337,28 +2337,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J2">
         <v>274</v>
@@ -2369,28 +2369,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J3">
         <v>280</v>
@@ -2401,28 +2401,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D4" s="2">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J4">
         <v>934</v>
@@ -2433,28 +2433,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D5" s="2">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J5">
         <v>972</v>
@@ -2465,28 +2465,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D6" s="2">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J6">
         <v>175</v>
@@ -2497,28 +2497,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J7">
         <v>179</v>
@@ -2529,28 +2529,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J8">
         <v>195</v>
@@ -2561,28 +2561,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J9">
         <v>189</v>
@@ -2593,28 +2593,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J10">
         <v>310</v>
@@ -2625,28 +2625,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J11">
         <v>310</v>
@@ -2657,28 +2657,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D12">
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I12" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J12">
         <v>474</v>
@@ -2689,28 +2689,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D13">
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H13" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J13">
         <v>473</v>
@@ -2721,28 +2721,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J14">
         <v>527</v>
@@ -2753,28 +2753,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H15" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J15">
         <v>504</v>
@@ -2785,28 +2785,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D16">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J16">
         <v>819</v>
@@ -2817,28 +2817,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I17" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J17">
         <v>651</v>
@@ -2849,28 +2849,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D18" s="2">
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J18">
         <v>905</v>
@@ -2881,28 +2881,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D19" s="2">
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J19">
         <v>828</v>
@@ -2913,28 +2913,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D20" s="2">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J20">
         <v>1023</v>
@@ -2945,28 +2945,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D21" s="2">
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H21" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J21">
         <v>968</v>
@@ -2977,28 +2977,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D22" s="2">
         <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H22" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J22">
         <v>511</v>
@@ -3009,28 +3009,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D23" s="2">
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J23">
         <v>496</v>
@@ -3041,28 +3041,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D24" s="2">
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I24" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J24">
         <v>539</v>
@@ -3073,28 +3073,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D25" s="2">
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I25" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J25">
         <v>551</v>
@@ -3105,28 +3105,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" s="2">
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I26" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J26">
         <v>599</v>
@@ -3137,28 +3137,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D27" s="2">
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="J27">
         <v>621</v>
@@ -3169,28 +3169,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D28" s="3">
         <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I28" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J28">
         <v>216</v>
@@ -3201,28 +3201,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D29" s="3">
         <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="J29">
         <v>205</v>
@@ -3233,28 +3233,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D30" s="3">
         <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H30" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I30" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J30">
         <v>553</v>
@@ -3265,28 +3265,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D31" s="3">
         <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I31" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J31">
         <v>569</v>
@@ -3297,28 +3297,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D32" s="2">
         <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H32" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I32" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J32">
         <v>555</v>
@@ -3329,28 +3329,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D33" s="2">
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F33">
         <v>2</v>
       </c>
       <c r="G33" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H33" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I33" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J33">
         <v>651</v>
@@ -3361,28 +3361,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
       </c>
       <c r="E34" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F34">
         <v>2</v>
       </c>
       <c r="G34" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H34" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I34" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J34">
         <v>2561</v>
@@ -3393,28 +3393,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D35" s="2">
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F35">
         <v>2</v>
       </c>
       <c r="G35" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I35" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="J35">
         <v>2599</v>
@@ -3425,28 +3425,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D36" s="2">
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I36" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J36">
         <v>3353</v>
@@ -3457,28 +3457,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D37" s="2">
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F37">
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H37" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I37" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J37">
         <v>3170</v>
@@ -3489,28 +3489,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D38" s="3">
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H38" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J38">
         <v>826</v>
@@ -3521,28 +3521,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D39" s="3">
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F39">
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H39" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J39">
         <v>807</v>
@@ -3553,28 +3553,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D40" s="3">
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F40">
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H40" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I40" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J40">
         <v>983</v>
@@ -3585,28 +3585,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D41" s="3">
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F41">
         <v>2</v>
       </c>
       <c r="G41" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H41" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I41" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J41">
         <v>834</v>
@@ -3617,28 +3617,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D42" s="3">
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F42">
         <v>2</v>
       </c>
       <c r="G42" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H42" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I42" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J42">
         <v>150</v>
@@ -3649,28 +3649,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D43" s="3">
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F43">
         <v>2</v>
       </c>
       <c r="G43" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H43" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I43" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J43">
         <v>162</v>
@@ -3681,28 +3681,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D44" s="2">
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F44">
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H44" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I44" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J44">
         <v>784</v>
@@ -3713,28 +3713,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D45" s="2">
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F45">
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I45" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J45">
         <v>832</v>
@@ -3745,28 +3745,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D46" s="2">
         <v>16</v>
       </c>
       <c r="E46" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F46">
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I46" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J46">
         <v>713</v>
@@ -3777,28 +3777,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D47" s="2">
         <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F47">
         <v>2</v>
       </c>
       <c r="G47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H47" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I47" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J47">
         <v>743</v>
@@ -3809,28 +3809,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D48" s="2">
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F48">
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J48">
         <v>563</v>
@@ -3841,28 +3841,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D49" s="2">
         <v>16</v>
       </c>
       <c r="E49" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F49">
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H49" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I49" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J49">
         <v>555</v>
@@ -3873,28 +3873,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D50" s="2">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F50">
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H50" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J50">
         <v>2838</v>
@@ -3905,28 +3905,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D51" s="2">
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F51">
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H51" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J51">
         <v>3042</v>
@@ -3937,28 +3937,28 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D52" s="2">
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F52">
         <v>2</v>
       </c>
       <c r="G52" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H52" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I52" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="J52">
         <v>459</v>
@@ -3969,28 +3969,28 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D53" s="2">
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F53">
         <v>2</v>
       </c>
       <c r="G53" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H53" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I53" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J53">
         <v>508</v>
@@ -4001,28 +4001,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D54" s="2">
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H54" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I54" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J54">
         <v>457</v>
@@ -4033,28 +4033,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D55" s="2">
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F55">
         <v>2</v>
       </c>
       <c r="G55" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H55" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J55">
         <v>464</v>
@@ -4065,28 +4065,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D56" s="3">
         <v>24</v>
       </c>
       <c r="E56" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F56">
         <v>2</v>
       </c>
       <c r="G56" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H56" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I56" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J56">
         <v>737</v>
@@ -4097,28 +4097,28 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D57" s="3">
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F57">
         <v>2</v>
       </c>
       <c r="G57" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H57" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J57">
         <v>617</v>
@@ -4129,28 +4129,28 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D58" s="2">
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F58">
         <v>2</v>
       </c>
       <c r="G58" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H58" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I58" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J58">
         <v>1343</v>
@@ -4161,28 +4161,28 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C59" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D59" s="2">
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F59">
         <v>2</v>
       </c>
       <c r="G59" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I59" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J59">
         <v>1376</v>
@@ -4193,28 +4193,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D60" s="2">
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F60">
         <v>2</v>
       </c>
       <c r="G60" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H60" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I60" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J60">
         <v>664</v>
@@ -4225,28 +4225,28 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D61" s="2">
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F61">
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H61" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I61" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J61">
         <v>617</v>
@@ -4257,28 +4257,28 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D62" s="2">
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F62">
         <v>2</v>
       </c>
       <c r="G62" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H62" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I62" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J62">
         <v>436</v>
@@ -4289,28 +4289,28 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D63" s="2">
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F63">
         <v>2</v>
       </c>
       <c r="G63" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H63" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J63">
         <v>495</v>
@@ -4321,28 +4321,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D64" s="2">
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F64">
         <v>2</v>
       </c>
       <c r="G64" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H64" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I64" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="J64">
         <v>272</v>
@@ -4353,28 +4353,28 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C65" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D65" s="2">
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F65">
         <v>2</v>
       </c>
       <c r="G65" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H65" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I65" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J65">
         <v>274</v>
@@ -4385,28 +4385,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D66" s="2">
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F66">
         <v>3</v>
       </c>
       <c r="G66" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H66" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I66" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J66">
         <v>4891</v>
@@ -4417,28 +4417,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D67" s="2">
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F67">
         <v>3</v>
       </c>
       <c r="G67" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H67" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I67" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J67">
         <v>4818</v>
@@ -4449,28 +4449,28 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D68">
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F68">
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H68" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I68" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J68">
         <v>2173</v>
@@ -4481,28 +4481,28 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D69">
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F69">
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H69" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I69" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J69">
         <v>1993</v>
@@ -4513,28 +4513,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D70" s="2">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F70">
         <v>3</v>
       </c>
       <c r="G70" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H70" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I70" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J70">
         <v>732</v>
@@ -4545,28 +4545,28 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D71" s="2">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F71">
         <v>3</v>
       </c>
       <c r="G71" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I71" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J71">
         <v>577</v>
@@ -4577,28 +4577,28 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D72" s="2">
         <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F72">
         <v>3</v>
       </c>
       <c r="G72" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H72" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I72" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J72">
         <v>608</v>
@@ -4609,28 +4609,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D73" s="2">
         <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F73">
         <v>3</v>
       </c>
       <c r="G73" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I73" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J73">
         <v>659</v>
@@ -4641,28 +4641,28 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D74" s="2">
         <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F74">
         <v>3</v>
       </c>
       <c r="G74" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H74" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I74" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J74">
         <v>1004</v>
@@ -4673,28 +4673,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D75" s="2">
         <v>8</v>
       </c>
       <c r="E75" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F75">
         <v>3</v>
       </c>
       <c r="G75" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H75" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I75" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J75">
         <v>830</v>
@@ -4705,28 +4705,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C76" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D76" s="2">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F76">
         <v>3</v>
       </c>
       <c r="G76" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H76" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I76" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J76">
         <v>3164</v>
@@ -4737,28 +4737,28 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D77" s="2">
         <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F77">
         <v>3</v>
       </c>
       <c r="G77" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H77" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I77" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J77">
         <v>3199</v>
@@ -4769,28 +4769,28 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D78" s="2">
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F78">
         <v>3</v>
       </c>
       <c r="G78" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H78" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I78" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J78">
         <v>1591</v>
@@ -4801,28 +4801,28 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C79" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D79" s="2">
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F79">
         <v>3</v>
       </c>
       <c r="G79" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H79" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I79" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J79">
         <v>1346</v>
@@ -4833,28 +4833,28 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D80" s="3">
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F80">
         <v>3</v>
       </c>
       <c r="G80" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H80" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I80" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J80">
         <v>2123</v>
@@ -4865,28 +4865,28 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D81" s="3">
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F81">
         <v>3</v>
       </c>
       <c r="G81" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H81" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I81" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J81">
         <v>2075</v>
@@ -4897,28 +4897,28 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C82" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D82" s="2">
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F82">
         <v>3</v>
       </c>
       <c r="G82" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H82" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I82" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J82">
         <v>7131</v>
@@ -4929,28 +4929,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C83" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D83" s="2">
         <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F83">
         <v>3</v>
       </c>
       <c r="G83" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H83" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I83" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J83">
         <v>7710</v>
@@ -4961,28 +4961,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D84" s="2">
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F84">
         <v>3</v>
       </c>
       <c r="G84" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H84" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="J84">
         <v>7131</v>
@@ -4993,28 +4993,28 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D85" s="2">
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F85">
         <v>3</v>
       </c>
       <c r="G85" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H85" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J85">
         <v>7710</v>
@@ -5025,28 +5025,28 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C86" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D86" s="2">
         <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F86">
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H86" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I86" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J86">
         <v>3669</v>
@@ -5057,28 +5057,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C87" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D87" s="2">
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F87">
         <v>3</v>
       </c>
       <c r="G87" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H87" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I87" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J87">
         <v>3769</v>
@@ -5089,28 +5089,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D88" s="2">
         <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F88">
         <v>3</v>
       </c>
       <c r="G88" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H88" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I88" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J88">
         <v>926</v>
@@ -5121,28 +5121,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D89" s="2">
         <v>13</v>
       </c>
       <c r="E89" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F89">
         <v>3</v>
       </c>
       <c r="G89" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H89" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I89" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="J89">
         <v>859</v>
@@ -5153,28 +5153,28 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C90" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D90" s="3">
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F90">
         <v>3</v>
       </c>
       <c r="G90" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H90" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I90" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="J90">
         <v>464</v>
@@ -5185,28 +5185,28 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C91" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D91" s="3">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F91">
         <v>3</v>
       </c>
       <c r="G91" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H91" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I91" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J91">
         <v>548</v>
@@ -5217,28 +5217,28 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D92" s="3">
         <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F92">
         <v>3</v>
       </c>
       <c r="G92" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H92" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I92" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J92">
         <v>735</v>
@@ -5249,28 +5249,28 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C93" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D93" s="3">
         <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F93">
         <v>3</v>
       </c>
       <c r="G93" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H93" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I93" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J93">
         <v>756</v>
@@ -5281,28 +5281,28 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C94" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D94" s="3">
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F94">
         <v>3</v>
       </c>
       <c r="G94" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H94" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I94" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J94">
         <v>324</v>
@@ -5313,28 +5313,28 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C95" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D95" s="3">
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F95">
         <v>3</v>
       </c>
       <c r="G95" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H95" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I95" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J95">
         <v>294</v>
@@ -5345,28 +5345,28 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C96" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D96" s="3">
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F96">
         <v>3</v>
       </c>
       <c r="G96" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H96" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I96" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J96">
         <v>419</v>
@@ -5377,28 +5377,28 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C97" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D97" s="3">
         <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F97">
         <v>3</v>
       </c>
       <c r="G97" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H97" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I97" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J97">
         <v>382</v>
@@ -5409,28 +5409,28 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C98" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D98" s="2">
         <v>8</v>
       </c>
       <c r="E98" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F98">
         <v>3</v>
       </c>
       <c r="G98" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H98" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I98" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J98">
         <v>7130</v>
@@ -5441,28 +5441,28 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C99" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D99" s="2">
         <v>8</v>
       </c>
       <c r="E99" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F99">
         <v>3</v>
       </c>
       <c r="G99" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H99" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I99" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="J99">
         <v>7541</v>
@@ -5473,28 +5473,28 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D100" s="2">
         <v>14</v>
       </c>
       <c r="E100" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F100">
         <v>3</v>
       </c>
       <c r="G100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H100" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I100" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J100">
         <v>4523</v>
@@ -5505,28 +5505,28 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D101" s="2">
         <v>14</v>
       </c>
       <c r="E101" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F101">
         <v>3</v>
       </c>
       <c r="G101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H101" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I101" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="J101">
         <v>4308</v>
@@ -5537,28 +5537,28 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D102" s="3">
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F102" s="2">
         <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H102" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I102" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="J102">
         <v>7012</v>
@@ -5569,28 +5569,28 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C103" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D103" s="3">
         <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F103" s="2">
         <v>4</v>
       </c>
       <c r="G103" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H103" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I103" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J103">
         <v>7392</v>
@@ -5601,28 +5601,28 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C104" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D104" s="3">
         <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F104">
         <v>3</v>
       </c>
       <c r="G104" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H104" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I104" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J104">
         <v>3871</v>
@@ -5633,28 +5633,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C105" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D105" s="3">
         <v>29</v>
       </c>
       <c r="E105" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F105">
         <v>3</v>
       </c>
       <c r="G105" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H105" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I105" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="J105">
         <v>3483</v>
@@ -5665,28 +5665,28 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C106" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D106" s="3">
         <v>29</v>
       </c>
       <c r="E106" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F106">
         <v>3</v>
       </c>
       <c r="G106" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H106" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I106" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J106">
         <v>1246</v>
@@ -5697,28 +5697,28 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C107" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D107" s="3">
         <v>29</v>
       </c>
       <c r="E107" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F107">
         <v>3</v>
       </c>
       <c r="G107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I107" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J107">
         <v>1356</v>
@@ -5729,28 +5729,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D108" s="2">
         <v>17</v>
       </c>
       <c r="E108" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F108">
         <v>3</v>
       </c>
       <c r="G108" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H108" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I108" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J108">
         <v>1423</v>
@@ -5761,28 +5761,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C109" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D109" s="2">
         <v>17</v>
       </c>
       <c r="E109" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F109">
         <v>3</v>
       </c>
       <c r="G109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I109" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J109">
         <v>1549</v>
@@ -5793,28 +5793,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C110" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D110" s="2">
         <v>17</v>
       </c>
       <c r="E110" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F110">
         <v>3</v>
       </c>
       <c r="G110" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H110" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I110" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J110">
         <v>430</v>
@@ -5825,28 +5825,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C111" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D111" s="2">
         <v>17</v>
       </c>
       <c r="E111" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F111">
         <v>3</v>
       </c>
       <c r="G111" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H111" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I111" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J111">
         <v>484</v>
@@ -5857,28 +5857,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D112" s="2">
         <v>17</v>
       </c>
       <c r="E112" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F112">
         <v>3</v>
       </c>
       <c r="G112" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H112" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I112" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J112">
         <v>320</v>
@@ -5889,28 +5889,28 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D113" s="2">
         <v>17</v>
       </c>
       <c r="E113" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F113">
         <v>3</v>
       </c>
       <c r="G113" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H113" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I113" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J113">
         <v>266</v>
@@ -5921,28 +5921,28 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C114" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D114" s="2">
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F114" s="2">
         <v>4</v>
       </c>
       <c r="G114" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H114" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I114" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J114">
         <v>717</v>
@@ -5953,28 +5953,28 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D115" s="2">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F115" s="2">
         <v>4</v>
       </c>
       <c r="G115" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H115" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I115" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J115">
         <v>684</v>
@@ -5985,28 +5985,28 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D116" s="2">
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F116" s="2">
         <v>4</v>
       </c>
       <c r="G116" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H116" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I116" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J116">
         <v>236</v>
@@ -6017,28 +6017,28 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D117" s="2">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F117" s="2">
         <v>4</v>
       </c>
       <c r="G117" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H117" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I117" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J117">
         <v>223</v>
@@ -6049,28 +6049,28 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C118" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D118" s="2">
         <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F118" s="2">
         <v>4</v>
       </c>
       <c r="G118" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H118" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I118" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J118">
         <v>284</v>
@@ -6081,28 +6081,28 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C119" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D119" s="2">
         <v>13</v>
       </c>
       <c r="E119" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F119" s="2">
         <v>4</v>
       </c>
       <c r="G119" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H119" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I119" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J119">
         <v>313</v>
@@ -6113,28 +6113,28 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D120" s="2">
         <v>9</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F120" s="2">
         <v>4</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J120" s="2">
         <v>52</v>
@@ -6145,28 +6145,28 @@
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D121" s="2">
         <v>9</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F121" s="2">
         <v>4</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J121" s="2">
         <v>42</v>
@@ -6177,28 +6177,28 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D122" s="2">
         <v>9</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F122" s="2">
         <v>4</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J122" s="2">
         <v>304</v>
@@ -6209,28 +6209,28 @@
         <v>122</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D123" s="2">
         <v>9</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F123" s="2">
         <v>4</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J123" s="2">
         <v>244</v>
@@ -6241,28 +6241,28 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D124" s="2">
         <v>13</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F124" s="2">
         <v>4</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J124" s="2">
         <v>154</v>
@@ -6273,28 +6273,28 @@
         <v>124</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D125" s="2">
         <v>13</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F125" s="2">
         <v>4</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J125" s="2">
         <v>153</v>
@@ -6305,28 +6305,28 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D126" s="2">
         <v>13</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F126" s="2">
         <v>4</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J126" s="2">
         <v>471</v>
@@ -6337,28 +6337,28 @@
         <v>126</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D127" s="2">
         <v>13</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F127" s="2">
         <v>4</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J127" s="2">
         <v>463</v>
@@ -6369,28 +6369,28 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D128" s="2">
         <v>7</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F128" s="2">
         <v>4</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J128" s="2">
         <v>622</v>
@@ -6401,28 +6401,28 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D129" s="2">
         <v>7</v>
       </c>
       <c r="E129" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F129" s="2">
         <v>4</v>
       </c>
       <c r="G129" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H129" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I129" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J129">
         <v>690</v>
@@ -6433,28 +6433,28 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D130" s="2">
         <v>7</v>
       </c>
       <c r="E130" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F130" s="2">
         <v>4</v>
       </c>
       <c r="G130" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H130" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I130" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J130">
         <v>1515</v>
@@ -6465,28 +6465,28 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D131" s="2">
         <v>7</v>
       </c>
       <c r="E131" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F131" s="2">
         <v>4</v>
       </c>
       <c r="G131" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H131" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="J131">
         <v>1503</v>
@@ -6497,28 +6497,28 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C132" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D132" s="2">
         <v>7</v>
       </c>
       <c r="E132" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F132" s="2">
         <v>4</v>
       </c>
       <c r="G132" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H132" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I132" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J132">
         <v>351</v>
@@ -6529,28 +6529,28 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D133" s="2">
         <v>7</v>
       </c>
       <c r="E133" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F133" s="2">
         <v>4</v>
       </c>
       <c r="G133" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H133" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I133" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J133">
         <v>359</v>
@@ -6561,28 +6561,28 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C134" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D134" s="2">
         <v>13</v>
       </c>
       <c r="E134" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F134" s="2">
         <v>4</v>
       </c>
       <c r="G134" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H134" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I134" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J134">
         <v>1283</v>
@@ -6593,28 +6593,28 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D135" s="2">
         <v>13</v>
       </c>
       <c r="E135" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F135" s="2">
         <v>4</v>
       </c>
       <c r="G135" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H135" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I135" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J135">
         <v>1339</v>
@@ -6625,28 +6625,28 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C136" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D136" s="2">
         <v>13</v>
       </c>
       <c r="E136" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F136" s="2">
         <v>4</v>
       </c>
       <c r="G136" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H136" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I136" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J136">
         <v>198</v>
@@ -6657,28 +6657,28 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C137" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D137" s="2">
         <v>13</v>
       </c>
       <c r="E137" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F137" s="2">
         <v>4</v>
       </c>
       <c r="G137" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H137" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I137" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J137">
         <v>161</v>
@@ -6689,28 +6689,28 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C138" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D138" s="3">
         <v>25</v>
       </c>
       <c r="E138" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F138" s="2">
         <v>4</v>
       </c>
       <c r="G138" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H138" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I138" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J138">
         <v>1226</v>
@@ -6721,28 +6721,28 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C139" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D139" s="3">
         <v>25</v>
       </c>
       <c r="E139" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F139" s="2">
         <v>4</v>
       </c>
       <c r="G139" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H139" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J139">
         <v>1252</v>
@@ -6753,28 +6753,28 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C140" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D140" s="3">
         <v>25</v>
       </c>
       <c r="E140" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F140" s="2">
         <v>4</v>
       </c>
       <c r="G140" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H140" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I140" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J140">
         <v>431</v>
@@ -6785,28 +6785,28 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C141" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D141" s="3">
         <v>25</v>
       </c>
       <c r="E141" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="F141" s="2">
         <v>4</v>
       </c>
       <c r="G141" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H141" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I141" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="J141">
         <v>405</v>
@@ -6817,28 +6817,28 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C142" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D142" s="2">
         <v>8</v>
       </c>
       <c r="E142" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F142" s="2">
         <v>4</v>
       </c>
       <c r="G142" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H142" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I142" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J142">
         <v>813</v>
@@ -6849,28 +6849,28 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C143" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D143" s="2">
         <v>8</v>
       </c>
       <c r="E143" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F143" s="2">
         <v>4</v>
       </c>
       <c r="G143" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H143" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I143" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J143">
         <v>718</v>
@@ -6881,28 +6881,28 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C144" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D144" s="3">
         <v>29</v>
       </c>
       <c r="E144" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F144" s="2">
         <v>4</v>
       </c>
       <c r="G144" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H144" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I144" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J144">
         <v>106</v>
@@ -6913,28 +6913,28 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C145" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D145" s="3">
         <v>29</v>
       </c>
       <c r="E145" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="F145" s="2">
         <v>4</v>
       </c>
       <c r="G145" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H145" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I145" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J145">
         <v>123</v>
@@ -6945,28 +6945,28 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C146" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D146" s="2">
         <v>20</v>
       </c>
       <c r="E146" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F146" s="3">
         <v>7</v>
       </c>
       <c r="G146" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H146" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I146" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J146">
         <v>4397</v>
@@ -6977,28 +6977,28 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D147" s="2">
         <v>20</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F147" s="3">
         <v>7</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J147" s="3">
         <v>3986</v>
@@ -7009,28 +7009,28 @@
         <v>147</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D148" s="2">
         <v>20</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F148" s="3">
         <v>7</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J148" s="3">
         <v>727</v>
@@ -7041,28 +7041,28 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D149" s="2">
         <v>20</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F149" s="3">
         <v>7</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J149" s="3">
         <v>844</v>
@@ -7073,28 +7073,28 @@
         <v>149</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D150" s="3">
         <v>21</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F150" s="3">
         <v>7</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J150" s="3">
         <v>2177</v>
@@ -7105,28 +7105,28 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D151" s="3">
         <v>21</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F151" s="3">
         <v>7</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J151" s="3">
         <v>1902</v>
@@ -7137,28 +7137,28 @@
         <v>151</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D152" s="2">
         <v>8</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F152" s="3">
         <v>7</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J152" s="3">
         <v>2301</v>
@@ -7169,28 +7169,28 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D153" s="2">
         <v>8</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F153" s="3">
         <v>7</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J153" s="3">
         <v>2466</v>
@@ -7201,28 +7201,28 @@
         <v>153</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D154" s="2">
         <v>8</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F154" s="3">
         <v>7</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J154" s="3">
         <v>3973</v>
@@ -7233,28 +7233,28 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D155" s="2">
         <v>8</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F155" s="3">
         <v>7</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J155" s="3">
         <v>3565</v>
@@ -7265,28 +7265,28 @@
         <v>155</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D156" s="2">
         <v>8</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F156" s="3">
         <v>7</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J156" s="3">
         <v>5434</v>
@@ -7297,28 +7297,28 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D157" s="2">
         <v>8</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F157" s="3">
         <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J157" s="3">
         <v>5741</v>
@@ -7329,28 +7329,28 @@
         <v>157</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D158" s="2">
         <v>8</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F158" s="3">
         <v>7</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="J158" s="3">
         <v>2990</v>
@@ -7361,28 +7361,28 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D159" s="2">
         <v>8</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F159" s="3">
         <v>7</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J159" s="3">
         <v>3148</v>
@@ -7393,28 +7393,28 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D160" s="2">
         <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F160" s="3">
         <v>7</v>
       </c>
       <c r="G160" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H160" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I160" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J160">
         <v>1879</v>
@@ -7425,28 +7425,28 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D161" s="2">
         <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F161" s="3">
         <v>7</v>
       </c>
       <c r="G161" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H161" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I161" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="J161">
         <v>1892</v>
@@ -7457,28 +7457,28 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D162" s="2">
         <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F162" s="3">
         <v>7</v>
       </c>
       <c r="G162" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H162" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I162" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J162">
         <v>2220</v>
@@ -7489,28 +7489,28 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C163" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D163" s="2">
         <v>8</v>
       </c>
       <c r="E163" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F163" s="3">
         <v>7</v>
       </c>
       <c r="G163" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H163" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I163" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J163">
         <v>2366</v>
@@ -7521,28 +7521,28 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D164" s="3">
         <v>30</v>
       </c>
       <c r="E164" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F164" s="3">
         <v>7</v>
       </c>
       <c r="G164" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H164" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I164" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J164">
         <v>2760</v>
@@ -7553,28 +7553,28 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C165" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D165" s="3">
         <v>30</v>
       </c>
       <c r="E165" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F165" s="3">
         <v>7</v>
       </c>
       <c r="G165" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H165" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I165" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J165">
         <v>2604</v>
@@ -7585,28 +7585,28 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D166" s="3">
         <v>30</v>
       </c>
       <c r="E166" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F166" s="3">
         <v>7</v>
       </c>
       <c r="G166" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H166" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I166" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J166">
         <v>1624</v>
@@ -7617,28 +7617,28 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C167" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D167" s="3">
         <v>30</v>
       </c>
       <c r="E167" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F167" s="3">
         <v>7</v>
       </c>
       <c r="G167" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H167" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I167" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J167">
         <v>1452</v>
@@ -7649,28 +7649,28 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C168" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D168" s="3">
         <v>30</v>
       </c>
       <c r="E168" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F168" s="3">
         <v>7</v>
       </c>
       <c r="G168" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H168" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I168" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J168">
         <v>6092</v>
@@ -7681,28 +7681,28 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C169" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D169" s="3">
         <v>30</v>
       </c>
       <c r="E169" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F169" s="3">
         <v>7</v>
       </c>
       <c r="G169" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H169" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I169" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J169">
         <v>6572</v>
@@ -7713,28 +7713,28 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C170" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D170" s="3">
         <v>30</v>
       </c>
       <c r="E170" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F170" s="3">
         <v>7</v>
       </c>
       <c r="G170" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H170" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I170" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="J170">
         <v>1100</v>
@@ -7745,28 +7745,28 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C171" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D171" s="3">
         <v>30</v>
       </c>
       <c r="E171" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F171" s="3">
         <v>7</v>
       </c>
       <c r="G171" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H171" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I171" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J171">
         <v>912</v>
@@ -7777,28 +7777,28 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C172" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D172">
         <v>2</v>
       </c>
       <c r="E172" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F172" s="2">
         <v>5</v>
       </c>
       <c r="G172" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H172" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I172" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J172">
         <v>2251</v>
@@ -7809,28 +7809,28 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C173" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D173">
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F173" s="2">
         <v>5</v>
       </c>
       <c r="G173" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H173" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I173" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="J173">
         <v>2663</v>
@@ -7841,28 +7841,28 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C174" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D174">
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F174" s="2">
         <v>5</v>
       </c>
       <c r="G174" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H174" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I174" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J174">
         <v>2783</v>
@@ -7873,28 +7873,28 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C175" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D175">
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F175" s="2">
         <v>5</v>
       </c>
       <c r="G175" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H175" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I175" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J175">
         <v>2746</v>
@@ -7905,28 +7905,28 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C176" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D176">
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F176" s="2">
         <v>5</v>
       </c>
       <c r="G176" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H176" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I176" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J176">
         <v>364</v>
@@ -7937,28 +7937,28 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D177">
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F177" s="2">
         <v>5</v>
       </c>
       <c r="G177" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H177" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I177" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J177">
         <v>375</v>
@@ -7969,28 +7969,28 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C178" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D178">
         <v>2</v>
       </c>
       <c r="E178" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F178" s="2">
         <v>5</v>
       </c>
       <c r="G178" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H178" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I178" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J178">
         <v>1724</v>
@@ -8001,28 +8001,28 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C179" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D179">
         <v>2</v>
       </c>
       <c r="E179" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F179" s="2">
         <v>5</v>
       </c>
       <c r="G179" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H179" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I179" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J179">
         <v>1660</v>
@@ -8033,28 +8033,28 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C180" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D180">
         <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F180" s="2">
         <v>5</v>
       </c>
       <c r="G180" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H180" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I180" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J180">
         <v>990</v>
@@ -8065,28 +8065,28 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C181" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D181">
         <v>2</v>
       </c>
       <c r="E181" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F181" s="2">
         <v>5</v>
       </c>
       <c r="G181" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H181" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I181" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J181">
         <v>1117</v>
@@ -8097,28 +8097,28 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C182" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D182" s="3">
         <v>23</v>
       </c>
       <c r="E182" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F182" s="2">
         <v>5</v>
       </c>
       <c r="G182" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H182" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I182" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="J182">
         <v>365</v>
@@ -8129,28 +8129,28 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C183" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D183" s="3">
         <v>23</v>
       </c>
       <c r="E183" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F183" s="2">
         <v>5</v>
       </c>
       <c r="G183" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H183" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I183" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J183">
         <v>356</v>
@@ -8161,28 +8161,28 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D184">
         <v>5</v>
       </c>
       <c r="E184" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F184" s="2">
         <v>5</v>
       </c>
       <c r="G184" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H184" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I184" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J184">
         <v>569</v>
@@ -8193,28 +8193,28 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D185">
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="F185" s="2">
         <v>5</v>
       </c>
       <c r="G185" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H185" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I185" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J185">
         <v>588</v>
@@ -8225,28 +8225,28 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C186" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D186" s="2">
         <v>7</v>
       </c>
       <c r="E186" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F186" s="2">
         <v>5</v>
       </c>
       <c r="G186" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H186" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I186" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J186">
         <v>1419</v>
@@ -8257,28 +8257,28 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C187" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D187" s="2">
         <v>7</v>
       </c>
       <c r="E187" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F187" s="2">
         <v>5</v>
       </c>
       <c r="G187" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H187" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I187" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="J187">
         <v>1469</v>
@@ -8289,28 +8289,28 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C188" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D188" s="2">
         <v>7</v>
       </c>
       <c r="E188" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F188" s="2">
         <v>5</v>
       </c>
       <c r="G188" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H188" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I188" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J188">
         <v>372</v>
@@ -8321,28 +8321,28 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C189" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D189" s="2">
         <v>7</v>
       </c>
       <c r="E189" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F189" s="2">
         <v>5</v>
       </c>
       <c r="G189" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H189" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I189" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J189">
         <v>372</v>
@@ -8353,28 +8353,28 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C190" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D190">
         <v>2</v>
       </c>
       <c r="E190" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F190" s="2">
         <v>5</v>
       </c>
       <c r="G190" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H190" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I190" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="J190">
         <v>1345</v>
@@ -8385,28 +8385,28 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C191" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D191">
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F191" s="2">
         <v>5</v>
       </c>
       <c r="G191" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H191" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I191" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J191">
         <v>1375</v>
@@ -8417,28 +8417,28 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C192" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D192" s="2">
         <v>14</v>
       </c>
       <c r="E192" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F192">
         <v>3</v>
       </c>
       <c r="G192" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H192" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I192" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J192">
         <v>1762</v>
@@ -8449,28 +8449,28 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C193" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D193" s="2">
         <v>14</v>
       </c>
       <c r="E193" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F193">
         <v>3</v>
       </c>
       <c r="G193" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H193" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I193" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J193">
         <v>1588</v>
@@ -8481,28 +8481,28 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C194" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D194" s="2">
         <v>7</v>
       </c>
       <c r="E194" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F194" s="2">
         <v>5</v>
       </c>
       <c r="G194" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H194" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I194" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="J194">
         <v>5189</v>
@@ -8513,28 +8513,28 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C195" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D195" s="2">
         <v>7</v>
       </c>
       <c r="E195" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F195" s="2">
         <v>5</v>
       </c>
       <c r="G195" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H195" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I195" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="J195">
         <v>4987</v>
@@ -8545,28 +8545,28 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C196" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D196" s="2">
         <v>7</v>
       </c>
       <c r="E196" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F196" s="2">
         <v>5</v>
       </c>
       <c r="G196" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H196" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I196" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J196">
         <v>717</v>
@@ -8577,28 +8577,28 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C197" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D197" s="2">
         <v>7</v>
       </c>
       <c r="E197" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F197" s="2">
         <v>5</v>
       </c>
       <c r="G197" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H197" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I197" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J197">
         <v>600</v>
@@ -8609,28 +8609,28 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C198" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D198" s="2">
         <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F198" s="2">
         <v>5</v>
       </c>
       <c r="G198" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H198" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I198" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="J198">
         <v>1803</v>
@@ -8641,28 +8641,28 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C199" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D199" s="2">
         <v>18</v>
       </c>
       <c r="E199" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F199" s="2">
         <v>5</v>
       </c>
       <c r="G199" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H199" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I199" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J199">
         <v>1976</v>
@@ -8673,28 +8673,28 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D200" s="3">
         <v>22</v>
       </c>
       <c r="E200" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F200" s="2">
         <v>5</v>
       </c>
       <c r="G200" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H200" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I200" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J200">
         <v>1532</v>
@@ -8705,28 +8705,28 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C201" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D201" s="3">
         <v>22</v>
       </c>
       <c r="E201" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F201" s="2">
         <v>5</v>
       </c>
       <c r="G201" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H201" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I201" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J201">
         <v>1462</v>
@@ -8737,28 +8737,28 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C202" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D202" s="3">
         <v>22</v>
       </c>
       <c r="E202" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F202" s="2">
         <v>5</v>
       </c>
       <c r="G202" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H202" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I202" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J202">
         <v>1124</v>
@@ -8769,28 +8769,28 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D203" s="3">
         <v>22</v>
       </c>
       <c r="E203" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F203" s="2">
         <v>5</v>
       </c>
       <c r="G203" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H203" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I203" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J203">
         <v>1230</v>
@@ -8801,28 +8801,28 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C204" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D204" s="3">
         <v>22</v>
       </c>
       <c r="E204" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F204" s="2">
         <v>5</v>
       </c>
       <c r="G204" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H204" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I204" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J204">
         <v>1244</v>
@@ -8833,28 +8833,28 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C205" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D205" s="3">
         <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F205" s="2">
         <v>5</v>
       </c>
       <c r="G205" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H205" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I205" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J205">
         <v>1246</v>
@@ -8865,28 +8865,28 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C206" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D206" s="3">
         <v>22</v>
       </c>
       <c r="E206" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F206" s="2">
         <v>5</v>
       </c>
       <c r="G206" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H206" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I206" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J206">
         <v>306</v>
@@ -8897,28 +8897,28 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C207" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D207" s="3">
         <v>22</v>
       </c>
       <c r="E207" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F207" s="2">
         <v>5</v>
       </c>
       <c r="G207" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H207" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I207" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="J207">
         <v>268</v>
@@ -8929,28 +8929,28 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C208" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D208" s="3">
         <v>22</v>
       </c>
       <c r="E208" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F208" s="2">
         <v>5</v>
       </c>
       <c r="G208" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H208" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I208" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="J208">
         <v>730</v>
@@ -8961,28 +8961,28 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C209" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D209" s="3">
         <v>22</v>
       </c>
       <c r="E209" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F209" s="2">
         <v>5</v>
       </c>
       <c r="G209" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H209" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I209" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="J209">
         <v>799</v>
@@ -8993,28 +8993,28 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D210" s="3">
         <v>22</v>
       </c>
       <c r="E210" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F210" s="2">
         <v>5</v>
       </c>
       <c r="G210" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H210" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I210" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="J210">
         <v>766</v>
@@ -9025,28 +9025,28 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C211" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D211" s="3">
         <v>22</v>
       </c>
       <c r="E211" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F211" s="2">
         <v>5</v>
       </c>
       <c r="G211" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H211" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I211" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J211">
         <v>732</v>
@@ -9057,28 +9057,28 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C212" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D212" s="3">
         <v>23</v>
       </c>
       <c r="E212" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F212" s="2">
         <v>5</v>
       </c>
       <c r="G212" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H212" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I212" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J212">
         <v>1111</v>
@@ -9089,28 +9089,28 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C213" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D213" s="3">
         <v>23</v>
       </c>
       <c r="E213" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F213" s="2">
         <v>5</v>
       </c>
       <c r="G213" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H213" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I213" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J213">
         <v>1046</v>
@@ -9121,28 +9121,28 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C214" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D214" s="3">
         <v>23</v>
       </c>
       <c r="E214" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F214" s="2">
         <v>5</v>
       </c>
       <c r="G214" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H214" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I214" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J214">
         <v>642</v>
@@ -9153,28 +9153,28 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C215" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D215" s="3">
         <v>23</v>
       </c>
       <c r="E215" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F215" s="2">
         <v>5</v>
       </c>
       <c r="G215" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H215" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I215" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J215">
         <v>611</v>
@@ -9185,28 +9185,28 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C216" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D216" s="3">
         <v>23</v>
       </c>
       <c r="E216" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F216" s="2">
         <v>5</v>
       </c>
       <c r="G216" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H216" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I216" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J216">
         <v>649</v>
@@ -9217,28 +9217,28 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C217" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D217" s="3">
         <v>23</v>
       </c>
       <c r="E217" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F217" s="2">
         <v>5</v>
       </c>
       <c r="G217" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H217" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I217" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J217">
         <v>620</v>
@@ -9249,28 +9249,28 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C218" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D218" s="3">
         <v>28</v>
       </c>
       <c r="E218" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F218" s="2">
         <v>6</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H218" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I218" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J218">
         <v>1228</v>
@@ -9281,28 +9281,28 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C219" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D219" s="3">
         <v>28</v>
       </c>
       <c r="E219" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F219" s="2">
         <v>6</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H219" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I219" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="J219">
         <v>1148</v>
@@ -9313,28 +9313,28 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C220" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D220" s="3">
         <v>28</v>
       </c>
       <c r="E220" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F220" s="2">
         <v>6</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H220" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I220" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="J220">
         <v>5195</v>
@@ -9345,28 +9345,28 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C221" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D221" s="3">
         <v>28</v>
       </c>
       <c r="E221" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F221" s="2">
         <v>6</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H221" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I221" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J221">
         <v>5100</v>
@@ -9377,28 +9377,28 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C222" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D222" s="3">
         <v>28</v>
       </c>
       <c r="E222" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F222" s="2">
         <v>6</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H222" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I222" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="J222">
         <v>929</v>
@@ -9409,28 +9409,28 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C223" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D223" s="3">
         <v>28</v>
       </c>
       <c r="E223" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F223" s="2">
         <v>6</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H223" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I223" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J223">
         <v>964</v>
@@ -9441,28 +9441,28 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C224" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D224" s="3">
         <v>28</v>
       </c>
       <c r="E224" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F224" s="2">
         <v>6</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H224" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I224" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J224">
         <v>39456</v>
@@ -9473,28 +9473,28 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D225" s="3">
         <v>28</v>
       </c>
       <c r="E225" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F225" s="2">
         <v>6</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H225" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I225" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J225">
         <v>39058</v>
@@ -9505,28 +9505,28 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C226" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D226" s="3">
         <v>28</v>
       </c>
       <c r="E226" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F226" s="2">
         <v>6</v>
       </c>
       <c r="G226" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H226" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I226" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J226">
         <v>5625</v>
@@ -9537,28 +9537,28 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C227" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D227" s="3">
         <v>28</v>
       </c>
       <c r="E227" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F227" s="2">
         <v>6</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H227" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I227" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J227">
         <v>5937</v>
@@ -9569,28 +9569,28 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C228" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D228" s="3">
         <v>28</v>
       </c>
       <c r="E228" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F228" s="2">
         <v>6</v>
       </c>
       <c r="G228" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H228" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I228" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J228">
         <v>483</v>
@@ -9601,28 +9601,28 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C229" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D229" s="3">
         <v>28</v>
       </c>
       <c r="E229" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F229" s="2">
         <v>6</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H229" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I229" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J229">
         <v>554</v>
@@ -9633,28 +9633,28 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C230" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D230" s="3">
         <v>28</v>
       </c>
       <c r="E230" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F230" s="2">
         <v>6</v>
       </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H230" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I230" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J230">
         <v>333</v>
@@ -9665,28 +9665,28 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C231" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D231" s="3">
         <v>28</v>
       </c>
       <c r="E231" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F231" s="2">
         <v>6</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H231" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I231" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="J231">
         <v>330</v>
@@ -9697,28 +9697,28 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C232" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D232" s="2">
         <v>15</v>
       </c>
       <c r="E232" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F232" s="2">
         <v>6</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H232" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I232" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J232">
         <v>8810</v>
@@ -9729,28 +9729,28 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C233" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D233" s="2">
         <v>15</v>
       </c>
       <c r="E233" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F233" s="2">
         <v>6</v>
       </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H233" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I233" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="J233">
         <v>8337</v>
@@ -9761,28 +9761,28 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C234" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D234" s="3">
         <v>28</v>
       </c>
       <c r="E234" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F234" s="2">
         <v>6</v>
       </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H234" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I234" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J234">
         <v>411</v>
@@ -9793,28 +9793,28 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C235" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D235" s="3">
         <v>28</v>
       </c>
       <c r="E235" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F235" s="2">
         <v>6</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H235" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I235" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="J235">
         <v>426</v>
